--- a/data/source_of_truth/Portfolio_Snapshot_History.xlsx
+++ b/data/source_of_truth/Portfolio_Snapshot_History.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,10 +3614,8 @@
           <t>G42</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="H41" t="n">
+        <v>2022</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3695,10 +3693,8 @@
           <t>G42 Investments</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H42" t="n">
+        <v>2020</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3776,10 +3772,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H43" t="n">
+        <v>2020</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3857,10 +3851,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H44" t="n">
+        <v>2021</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3938,10 +3930,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H45" t="n">
+        <v>2019</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4017,10 +4007,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H46" t="n">
+        <v>2021</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4098,10 +4086,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H47" t="n">
+        <v>2019</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4177,10 +4163,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H48" t="n">
+        <v>2021</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4258,10 +4242,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H49" t="n">
+        <v>2019</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4337,10 +4319,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H50" t="n">
+        <v>2021</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4416,10 +4396,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="H51" t="n">
+        <v>2023</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4497,10 +4475,8 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="H52" t="n">
+        <v>2022</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4578,10 +4554,8 @@
           <t>Core42</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H53" t="n">
+        <v>2024</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4659,10 +4633,8 @@
           <t>G42 Capital</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="H54" t="n">
+        <v>2026</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4738,10 +4710,8 @@
           <t>G42 Capital</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H55" t="n">
+        <v>2024</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4819,10 +4789,8 @@
           <t>G42 Capital</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H56" t="n">
+        <v>2024</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4900,10 +4868,8 @@
           <t>G42 Capital</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H57" t="n">
+        <v>2025</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4981,10 +4947,8 @@
           <t>G42 Capital</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="H58" t="n">
+        <v>2025</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -5062,10 +5026,8 @@
           <t>G42 Capital</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H59" t="n">
+        <v>2024</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5141,10 +5103,8 @@
           <t>G42 Investments</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H60" t="n">
+        <v>2021</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5222,10 +5182,8 @@
           <t>G42 Investments</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="H61" t="n">
+        <v>2022</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5303,10 +5261,8 @@
           <t>G42 Investments</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H62" t="n">
+        <v>2020</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5384,10 +5340,8 @@
           <t>G42 Investments</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="H63" t="n">
+        <v>2023</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5465,10 +5419,8 @@
           <t>G42 Investments</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H64" t="n">
+        <v>2020</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5546,10 +5498,8 @@
           <t>G42 Investments</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="H65" t="n">
+        <v>2022</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5627,10 +5577,8 @@
           <t>G42 Holding</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H66" t="n">
+        <v>2024</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5708,10 +5656,8 @@
           <t>G42 Holding</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H67" t="n">
+        <v>2024</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5789,10 +5735,8 @@
           <t>G42 Holding</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H68" t="n">
+        <v>2024</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5870,10 +5814,8 @@
           <t>G42 Holding</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="H69" t="n">
+        <v>2024</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5933,12 +5875,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Applied AI Corporation Limited</t>
+          <t>MGX I LP + Denali</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5948,53 +5890,39 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>2024</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>A Prefs</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>15</v>
+        <v>1559.79804</v>
       </c>
       <c r="K70" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1559.79804</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>38.46473015</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>23.46473015</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2.564315343333333</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0.379698656873341</v>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Marked up, being held at 2.27X as per the last round</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6019,7 +5947,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beyond Limits</t>
+          <t>Applied AI Corporation Limited</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6032,21 +5960,19 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H71" t="n">
+        <v>2022</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>C Prefs</t>
+          <t>A Prefs</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -6055,16 +5981,16 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>21.7</v>
+        <v>38.46473015</v>
       </c>
       <c r="O71" t="n">
-        <v>-68.3</v>
+        <v>23.46473015</v>
       </c>
       <c r="P71" t="n">
-        <v>0.2411111111111111</v>
+        <v>2.564315343333333</v>
       </c>
       <c r="Q71" t="n">
-        <v>-0.2038134167490631</v>
+        <v>0.379698656873341</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -6073,7 +5999,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Ardent Dec'25 | 50% haircut recent convertible price during Q4'25</t>
+          <t>Marked up, being held at 2.27X as per the last round</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6026,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc (1)</t>
+          <t>Beyond Limits</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6113,39 +6039,37 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H72" t="n">
+        <v>2020</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Class A/B</t>
+          <t>C Prefs</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>39.99998336</v>
+        <v>90</v>
       </c>
       <c r="K72" t="n">
-        <v>39.99998335999999</v>
+        <v>90</v>
       </c>
       <c r="L72" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>286.4823928099999</v>
+        <v>21.7</v>
       </c>
       <c r="O72" t="n">
-        <v>246.4824094499999</v>
+        <v>-68.3</v>
       </c>
       <c r="P72" t="n">
-        <v>7.162062799668123</v>
+        <v>0.2411111111111111</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.5091940466191891</v>
+        <v>-0.2038134167490631</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -6154,7 +6078,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Marked to the latest round</t>
+          <t>Ardent Dec'25 | 50% haircut recent convertible price during Q4'25</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6105,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>E-line Ventures LLC</t>
+          <t>Cerebras Systems Inc (1)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6194,39 +6118,37 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="H73" t="n">
+        <v>2021</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>B Prefs</t>
+          <t>Class A/B</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>6</v>
+        <v>39.99998336</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>7.1</v>
+        <v>286.4823928099999</v>
       </c>
       <c r="O73" t="n">
-        <v>1.1</v>
+        <v>246.4824094499999</v>
       </c>
       <c r="P73" t="n">
-        <v>1.183333333333333</v>
+        <v>7.162062799668123</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.059274505967036</v>
+        <v>0.5091940466191891</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -6235,7 +6157,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Ardent Valuation as of 31 Dec 25</t>
+          <t>Marked to the latest round</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6184,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Endless Studios LLC</t>
+          <t>E-line Ventures LLC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6275,21 +6197,19 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="H74" t="n">
+        <v>2023</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>A Pref Units</t>
+          <t>B Prefs</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -6298,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="O74" t="n">
-        <v>-1.5</v>
+        <v>1.1</v>
       </c>
       <c r="P74" t="n">
-        <v>0.8125</v>
+        <v>1.183333333333333</v>
       </c>
       <c r="Q74" t="n">
-        <v>-0.05616841430472284</v>
+        <v>0.059274505967036</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -6343,7 +6263,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Flyr Inc</t>
+          <t>Endless Studios LLC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6356,21 +6276,19 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H75" t="n">
+        <v>2021</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>B-1,2 Prefs</t>
+          <t>A Pref Units</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -6379,16 +6297,16 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14.6</v>
+        <v>6.5</v>
       </c>
       <c r="O75" t="n">
-        <v>4.6</v>
+        <v>-1.5</v>
       </c>
       <c r="P75" t="n">
-        <v>1.46</v>
+        <v>0.8125</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.05695277639397291</v>
+        <v>-0.05616841430472284</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -6397,7 +6315,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>As per the recent fund raise for Series D</t>
+          <t>Ardent Valuation as of 31 Dec 25</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6342,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Heygears</t>
+          <t>Flyr Inc</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6437,21 +6355,19 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H76" t="n">
+        <v>2019</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Registered Capital</t>
+          <t>B-1,2 Prefs</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -6460,16 +6376,16 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>71.91884647972564</v>
+        <v>14.6</v>
       </c>
       <c r="O76" t="n">
-        <v>11.91884647972564</v>
+        <v>4.6</v>
       </c>
       <c r="P76" t="n">
-        <v>1.198647441328761</v>
+        <v>1.46</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.03249740083723869</v>
+        <v>0.05695277639397291</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -6478,7 +6394,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Priced round at RMB 141.2 per share | Mar'26</t>
+          <t>As per the recent fund raise for Series D</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6421,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ONT plc</t>
+          <t>Heygears</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6518,21 +6434,19 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H77" t="n">
+        <v>2020</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Ordinary Shares</t>
+          <t>Registered Capital</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>141.4702596743665</v>
+        <v>60</v>
       </c>
       <c r="K77" t="n">
-        <v>141.4702596743665</v>
+        <v>60</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -6541,16 +6455,16 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>67.52236550879999</v>
+        <v>71.91884647972564</v>
       </c>
       <c r="O77" t="n">
-        <v>-73.94789416556648</v>
+        <v>11.91884647972564</v>
       </c>
       <c r="P77" t="n">
-        <v>0.4772901786157859</v>
+        <v>1.198647441328761</v>
       </c>
       <c r="Q77" t="n">
-        <v>-0.1135171173653592</v>
+        <v>0.03249740083723869</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -6559,7 +6473,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Listed &amp; marked to market</t>
+          <t xml:space="preserve"> Priced round at RMB 141.2 per share | Mar'26</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6500,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tools for Humanity Corporation</t>
+          <t>ONT plc</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6599,21 +6513,19 @@
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="H78" t="n">
+        <v>2020</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>C Prefs</t>
+          <t>Ordinary Shares</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>14.99999894</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="K78" t="n">
-        <v>14.99999894</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -6622,16 +6534,16 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>1.2</v>
+        <v>67.52236550879999</v>
       </c>
       <c r="O78" t="n">
-        <v>-13.79999894</v>
+        <v>-73.94789416556648</v>
       </c>
       <c r="P78" t="n">
-        <v>0.08000000565333373</v>
+        <v>0.4772901786157859</v>
       </c>
       <c r="Q78" t="n">
-        <v>-0.5486080580793249</v>
+        <v>-0.1135171173653592</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -6640,7 +6552,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Ardent Valuation as of 31 Dec 25</t>
+          <t>Listed &amp; marked to market</t>
         </is>
       </c>
     </row>
@@ -6667,59 +6579,3336 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>Tools for Humanity Corporation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>C Prefs</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="K79" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-13.79999894</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.08000000565333373</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>-0.5486080580793249</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Ardent Valuation as of 31 Dec 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>eSpace</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Unrealized</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H80" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>B Prefs</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>15</v>
+      </c>
+      <c r="K80" t="n">
+        <v>15</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>230.00750916</v>
+      </c>
+      <c r="O80" t="n">
+        <v>215.00750916</v>
+      </c>
+      <c r="P80" t="n">
+        <v>15.333833944</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.101240687453752</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marked up, as converted as per the latest priced round </t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Honor Device Co Ltd</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>G42</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Equity-TBC</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>800</v>
+      </c>
+      <c r="K81" t="n">
+        <v>800</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>802.8</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>2.799999999999955</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1.0035</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.002935923132959731</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Exited at 1.0X</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Sinovation Disrupt Fund, L.P.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>50</v>
+      </c>
+      <c r="K82" t="n">
+        <v>24.959693</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>25.40352135</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.4438283500000004</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.017781803245737</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.007642245213040634</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Esyasoft Holding</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Convertible Note</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>5</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P83" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.3609176591261273</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Exited at $5m (10th May) | Residual value = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Esyasoft Holding (Debt)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.411765</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.411765</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.47078465</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.05901965000000003</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.143333333333333</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.09898188170804081</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Exited. Received payment of $470,784.65 ($411K+$59K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Glass Earth Holdings LLC</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Written-off</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Promissory Note</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>8</v>
+      </c>
+      <c r="K85" t="n">
+        <v>8</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>In default</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Instadeep Limited</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>B Prefs</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J86" t="n">
+        <v>5.023720198477434</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5.023720198477434</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>7.942192529999999</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>2.918472331522565</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.580938471136805</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.3280349790276135</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Exited at 1.56X | Residual Value = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Jollychic Holding Limited</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Written-off</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>C+ Prefs</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>65</v>
+      </c>
+      <c r="K87" t="n">
+        <v>65</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-65</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Exited/Liquidated</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Jysan Technologies</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>A (Ordinary Shares)</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>20</v>
+      </c>
+      <c r="K88" t="n">
+        <v>20</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.09882450563949773</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Exited at $24.5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Mena Mobile Inc</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Written-off</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>B Prefs</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>8</v>
+      </c>
+      <c r="K89" t="n">
+        <v>8</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>As per 3rd Party | Ardent Estimates | Equity written off</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Mena Mobile Inc (Debt)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Written-off</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>2.353982</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2.353982</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>-2.353982</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>In liquidation</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>WLD Tokens</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Tokens</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0.006875</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.006875</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>100</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>99.99312500000001</v>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="n">
+        <v>727.8222082232667</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>source: coinmarket cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>X-fusion</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Equity-TBC</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>493.5009562</v>
+      </c>
+      <c r="K92" t="n">
+        <v>493.5009562</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>403</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>-90.50095619999996</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.8166144258425249</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>-0.1075288453179172</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exited at 0.82X </t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Core42 Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>School Hack (AIREV Holding Limited)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Core42</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Preferred Shares</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>-2.543922105633999e-17</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Held at cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>G42 Capital SPV RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Cerebras Systems Inc (2)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>G42 Capital</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Class A/B</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0.03513491000000001</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.03513491000000001</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>647.32558184</v>
+      </c>
+      <c r="O94" t="n">
+        <v>647.29044693</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Marked to the latest round Q126</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>G42 Capital SPV RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Inveniam Ltd</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>G42 Capital</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>100</v>
+      </c>
+      <c r="K95" t="n">
+        <v>100</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.499965</v>
+      </c>
+      <c r="N95" t="n">
+        <v>100</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.4999650000000031</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1.00499965</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.002940024332733333</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Held at cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>G42 Capital SPV RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Life Biosciences LLC</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>G42 Capital</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>D Prefs</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>40</v>
+      </c>
+      <c r="K96" t="n">
+        <v>40</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>40.9473937147</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.9473937146999987</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1.0236848428675</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.01127988670501709</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Held at cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>G42 Capital SPV RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Liquid AI</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>G42 Capital</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>60.81986292</v>
+      </c>
+      <c r="K97" t="n">
+        <v>60.81986292</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>66.59918374999999</v>
+      </c>
+      <c r="O97" t="n">
+        <v>5.779320829999996</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1.095023575400061</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.1246650272180429</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Held at cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>G42 Capital SPV RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Neuralink</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>G42 Capital</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Series E</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>49.9999995</v>
+      </c>
+      <c r="K98" t="n">
+        <v>49.9999995</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>50</v>
+      </c>
+      <c r="O98" t="n">
+        <v>4.999999987376214e-07</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1.00000001</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>8.649289246403672e-09</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Held at cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>G42 Capital SPV RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Verses AI Inc</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>G42 Capital</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Ordinary Shares</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>10</v>
+      </c>
+      <c r="K99" t="n">
+        <v>10</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Listed &amp; marked to market</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Acies Investments Fund I, L.P.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>17.1125</v>
+      </c>
+      <c r="K100" t="n">
+        <v>15.726388</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1.386113</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>14.034903</v>
+      </c>
+      <c r="O100" t="n">
+        <v>-1.691485</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.8924428800815546</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>-0.02935277732578557</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Q2'26 capital account statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>DriveNets</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Partially Realized</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Equity-TBC</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>300</v>
+      </c>
+      <c r="K101" t="n">
+        <v>300</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>84.80448613999999</v>
+      </c>
+      <c r="N101" t="n">
+        <v>497.5350567066</v>
+      </c>
+      <c r="O101" t="n">
+        <v>282.3395428465999</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1.941131809488666</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.1745459048509513</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Priced round at US$7.35 per share | Mar'26</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>New Space Capital Fund I</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>26.7823643474</v>
+      </c>
+      <c r="K102" t="n">
+        <v>16.87804819658807</v>
+      </c>
+      <c r="L102" t="n">
+        <v>9.904316150811932</v>
+      </c>
+      <c r="M102" t="n">
+        <v>6.7779339379808</v>
+      </c>
+      <c r="N102" t="n">
+        <v>57.15618120708599</v>
+      </c>
+      <c r="O102" t="n">
+        <v>47.05606694847872</v>
+      </c>
+      <c r="P102" t="n">
+        <v>3.788004063052219</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.1994548830844582</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Q2'26 Limited Partner Statement (NewSpace Capital Fund S.C.S., for G42 Investments AI Holding Limited)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>New Space Capital GP Com SCSp</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>2.705882352941176</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2.705882352941176</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>6.786449200178311</v>
+      </c>
+      <c r="O103" t="n">
+        <v>4.080566847237135</v>
+      </c>
+      <c r="P103" t="n">
+        <v>2.508035573978941</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.1156541964277766</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Q3'25  capital account statement of GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>North Summit Capital Fund</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>83.361611</v>
+      </c>
+      <c r="K104" t="n">
+        <v>83.361611</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>7.875571</v>
+      </c>
+      <c r="N104" t="n">
+        <v>72.566225</v>
+      </c>
+      <c r="O104" t="n">
+        <v>-2.919815</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.9649741054068641</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>-0.01242878543472056</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Q1'26  capital account statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>vTv Therapeutics Inc.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Ordinary Shares</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>24.53125</v>
+      </c>
+      <c r="K105" t="n">
+        <v>24.53125</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>8.309024000000001</v>
+      </c>
+      <c r="O105" t="n">
+        <v>-16.222226</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.3387118063694268</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>-0.246693162941984</v>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Listed &amp; marked to market</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>MGX 1 Strategic Co-invest</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>296.60196</v>
+      </c>
+      <c r="K106" t="n">
+        <v>294.251545</v>
+      </c>
+      <c r="L106" t="n">
+        <v>2.350415</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1180.373331</v>
+      </c>
+      <c r="O106" t="n">
+        <v>886.1217859999999</v>
+      </c>
+      <c r="P106" t="n">
+        <v>4.011443103892623</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1.148844186667105</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Q2'26 capital account statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>MGX Group Holding 1 Ltd (GP)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>25</v>
+      </c>
+      <c r="K107" t="n">
+        <v>25</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>25</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>-3.037872421094163e-17</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Q4'25  capital account statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>MGX I Denali Holding LP</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>35.652964</v>
+      </c>
+      <c r="K108" t="n">
+        <v>35.652964</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>62.794035</v>
+      </c>
+      <c r="O108" t="n">
+        <v>27.141071</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1.761257072483511</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.7757347398913037</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Q2'26 capital account statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>MGX I LP</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>1524.145076</v>
+      </c>
+      <c r="K109" t="n">
+        <v>350.846909</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1173.298167</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>948.484252</v>
+      </c>
+      <c r="O109" t="n">
+        <v>597.637343</v>
+      </c>
+      <c r="P109" t="n">
+        <v>2.703413448057483</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>MGX I LP + Denali</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>1559.79804</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1559.79804</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Applied AI Corporation Limited</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>A Prefs</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
         <v>15</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K111" t="n">
         <v>15</v>
       </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>38.46473015</v>
+      </c>
+      <c r="O111" t="n">
+        <v>23.46473015</v>
+      </c>
+      <c r="P111" t="n">
+        <v>2.564315343333333</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.379698656873341</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Marked up, being held at 2.27X as per the last round</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Beyond Limits</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>C Prefs</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>90</v>
+      </c>
+      <c r="K112" t="n">
+        <v>90</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="O112" t="n">
+        <v>-68.3</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.2411111111111111</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>-0.2038134167490631</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Ardent Dec'25 | 50% haircut recent convertible price during Q4'25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Cerebras Systems Inc (1)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Class A/B</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>39.99998335999999</v>
+      </c>
+      <c r="K113" t="n">
+        <v>39.99998335999999</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>265.62083464</v>
+      </c>
+      <c r="O113" t="n">
+        <v>225.62085128</v>
+      </c>
+      <c r="P113" t="n">
+        <v>6.640523628457831</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.5091940466191891</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Marked to the latest round</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>E-line Ventures LLC</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>B Prefs</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>6</v>
+      </c>
+      <c r="K114" t="n">
+        <v>6</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1.183333333333333</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.059274505967036</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Ardent Valuation as of 31 Dec 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Endless Studios LLC</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>A Pref Units</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>8</v>
+      </c>
+      <c r="K115" t="n">
+        <v>8</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O115" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>-0.05616841430472284</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Ardent Valuation as of 31 Dec 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Flyr Inc</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>B-1,2 Prefs</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>10</v>
+      </c>
+      <c r="K116" t="n">
+        <v>10</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="O116" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.05695277639397291</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>As per the recent fund raise for Series D</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Heygears</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Registered Capital</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>60</v>
+      </c>
+      <c r="K117" t="n">
+        <v>60</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>71.91884647972564</v>
+      </c>
+      <c r="O117" t="n">
+        <v>11.91884647972564</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.198647441328761</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.03249740083723869</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Priced round at RMB 141.2 per share | Mar'26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ONT plc</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Ordinary Shares</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>141.4702596743665</v>
+      </c>
+      <c r="K118" t="n">
+        <v>141.4702596743665</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>105.22733244336</v>
+      </c>
+      <c r="O118" t="n">
+        <v>-36.2429272310065</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.743812393400353</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>-0.1135171173653592</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Listed &amp; marked to market</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Tools for Humanity Corporation</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>C Prefs</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="K119" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O119" t="n">
+        <v>-13.79999894</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.08000000565333373</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>-0.5486080580793249</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Ardent Valuation as of 31 Dec 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>eSpace</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>B Prefs</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>15</v>
+      </c>
+      <c r="K120" t="n">
+        <v>15</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
         <v>230.00750916</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O120" t="n">
         <v>215.00750916</v>
       </c>
-      <c r="P79" t="n">
+      <c r="P120" t="n">
         <v>15.333833944</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="Q120" t="n">
         <v>1.101240687453752</v>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="R120" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S120" t="inlineStr">
         <is>
           <t xml:space="preserve">Marked up, as converted as per the latest priced round </t>
         </is>
@@ -6839,12 +10028,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6920,12 +10109,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7001,12 +10190,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7082,12 +10271,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7163,12 +10352,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7207,25 +10396,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>39.99998336</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="K6" t="n">
         <v>39.99998335999999</v>
       </c>
       <c r="L6" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>286.4823928099999</v>
+        <v>265.62083464</v>
       </c>
       <c r="O6" t="n">
-        <v>246.4824094499999</v>
+        <v>225.62085128</v>
       </c>
       <c r="P6" t="n">
-        <v>7.162062799668123</v>
+        <v>6.640523628457831</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5091940466191891</v>
@@ -7244,12 +10433,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7325,12 +10514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7406,12 +10595,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7487,12 +10676,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7543,13 +10732,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>67.52236550879999</v>
+        <v>105.22733244336</v>
       </c>
       <c r="O10" t="n">
-        <v>-73.94789416556648</v>
+        <v>-36.2429272310065</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4772901786157859</v>
+        <v>0.743812393400353</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.1135171173653592</v>
@@ -7568,12 +10757,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7649,12 +10838,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7708,10 +10897,10 @@
         <v>497.5350567066</v>
       </c>
       <c r="O12" t="n">
-        <v>282.3395428466</v>
+        <v>282.3395428465999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.941131809488667</v>
+        <v>1.941131809488666</v>
       </c>
       <c r="Q12" t="n">
         <v>0.1745459048509513</v>
@@ -7730,12 +10919,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7786,13 +10975,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8.399903950000001</v>
+        <v>8.309024000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-16.13134605</v>
+        <v>-16.222226</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3424164667515924</v>
+        <v>0.3387118063694268</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.246693162941984</v>
@@ -7811,12 +11000,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7867,13 +11056,13 @@
         <v>7.875571</v>
       </c>
       <c r="N14" t="n">
-        <v>69.98505299999999</v>
+        <v>72.566225</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.500987000000009</v>
+        <v>-2.919815</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9340105483326131</v>
+        <v>0.9649741054068641</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.01242878543472056</v>
@@ -7892,12 +11081,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7936,25 +11125,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>26.7196311505</v>
+        <v>26.7823643474</v>
       </c>
       <c r="K15" t="n">
-        <v>17.80166535</v>
+        <v>16.87804819658807</v>
       </c>
       <c r="L15" t="n">
-        <v>8.917965800499999</v>
+        <v>9.904316150811932</v>
       </c>
       <c r="M15" t="n">
-        <v>6.50828684</v>
+        <v>6.7779339379808</v>
       </c>
       <c r="N15" t="n">
-        <v>54.1676251908</v>
+        <v>57.15618120708599</v>
       </c>
       <c r="O15" t="n">
-        <v>42.87424668079999</v>
+        <v>47.05606694847872</v>
       </c>
       <c r="P15" t="n">
-        <v>3.408440212634375</v>
+        <v>3.788004063052219</v>
       </c>
       <c r="Q15" t="n">
         <v>0.1994548830844582</v>
@@ -7973,12 +11162,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8026,16 +11215,16 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.20616173</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.858379496274193</v>
+        <v>6.786449200178311</v>
       </c>
       <c r="O16" t="n">
-        <v>1.358658873333016</v>
+        <v>4.080566847237135</v>
       </c>
       <c r="P16" t="n">
-        <v>1.502113061883941</v>
+        <v>2.508035573978941</v>
       </c>
       <c r="Q16" t="n">
         <v>0.1156541964277766</v>
@@ -8054,12 +11243,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8101,10 +11290,10 @@
         <v>17.1125</v>
       </c>
       <c r="K17" t="n">
-        <v>15.7263875</v>
+        <v>15.726388</v>
       </c>
       <c r="L17" t="n">
-        <v>1.386112500000001</v>
+        <v>1.386113</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -8113,10 +11302,10 @@
         <v>14.034903</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6914845</v>
+        <v>-1.691485</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8924429084556132</v>
+        <v>0.8924428800815546</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.02935277732578557</v>
@@ -8135,12 +11324,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8216,12 +11405,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8295,12 +11484,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8376,12 +11565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8420,13 +11609,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>60.81986291</v>
+        <v>60.81986292</v>
       </c>
       <c r="K21" t="n">
         <v>60.81986292</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.000000082740371e-08</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -8457,12 +11646,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8538,12 +11727,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8594,14 +11783,12 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>698.16579661</v>
+        <v>647.32558184</v>
       </c>
       <c r="O23" t="n">
-        <v>698.1306617</v>
-      </c>
-      <c r="P23" t="n">
-        <v>19871</v>
-      </c>
+        <v>647.29044693</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
@@ -8617,12 +11804,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8698,12 +11885,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8718,7 +11905,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MGX I LP</t>
+          <t>MGX I Denali Holding LP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8742,28 +11929,28 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1524.145076</v>
+        <v>35.652964</v>
       </c>
       <c r="K25" t="n">
-        <v>437.0838774046402</v>
+        <v>35.652964</v>
       </c>
       <c r="L25" t="n">
-        <v>1087.06119859536</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>91.05395026651516</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>948.484252</v>
+        <v>62.794035</v>
       </c>
       <c r="O25" t="n">
-        <v>602.454324861875</v>
+        <v>27.141071</v>
       </c>
       <c r="P25" t="n">
-        <v>2.378349456491481</v>
+        <v>1.761257072483511</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.608035438909162</v>
+        <v>0.7757347398913037</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -8779,12 +11966,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8799,7 +11986,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MGX I Denali Holding LP</t>
+          <t>MGX 1 Strategic Co-invest</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8823,28 +12010,28 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35.652964</v>
+        <v>296.60196</v>
       </c>
       <c r="K26" t="n">
-        <v>27.67275042834596</v>
+        <v>294.251545</v>
       </c>
       <c r="L26" t="n">
-        <v>7.980213571654037</v>
+        <v>2.350415</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>62.794035</v>
+        <v>1180.373331</v>
       </c>
       <c r="O26" t="n">
-        <v>35.12128457165404</v>
+        <v>886.1217859999999</v>
       </c>
       <c r="P26" t="n">
-        <v>2.269164937637653</v>
+        <v>4.011443103892623</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7757347398913037</v>
+        <v>1.148844186667105</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -8860,739 +12047,735 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MGX Group Holding 1 Ltd (GP)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-3.037872421094163e-17</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MGX 1 Strategic Co-invest</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>G42 Holding</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>296.60196</v>
-      </c>
-      <c r="K27" t="n">
-        <v>562.499557575</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-265.897597575</v>
-      </c>
-      <c r="M27" t="n">
-        <v>249.9999988</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1180.373331</v>
-      </c>
-      <c r="O27" t="n">
-        <v>867.8737722249999</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.542887919710556</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.148844186667105</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Q2'26 capital account statement</t>
+          <t>Q4'25  capital account statement</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>WLD Tokens</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Tokens</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.006875</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.006875</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>100</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>99.99312500000001</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>727.8222082232667</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MGX Group Holding 1 Ltd (GP)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>G42 Holding</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>25</v>
-      </c>
-      <c r="K28" t="n">
-        <v>25</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>25</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-3.037872421094163e-17</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Q4'25  capital account statement</t>
+          <t>source: coinmarket cap</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>X-fusion</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Equity-TBC</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>493.5009562</v>
+      </c>
+      <c r="K29" t="n">
+        <v>493.5009562</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>403</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-90.50095619999996</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8166144258425249</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.1075288453179172</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>WLD Tokens</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Tokens</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0.006875</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.006875</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>99.99312500000001</v>
-      </c>
-      <c r="P29" t="n">
-        <v>14545.45454545455</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>727.8222082232667</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>source: coinmarket cap</t>
+          <t xml:space="preserve">Exited at 0.82X </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mena Mobile Inc (Debt)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Written-off</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>2.353982</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.353982</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-2.353982</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>X-fusion</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Equity-TBC</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>493.5009562</v>
-      </c>
-      <c r="K30" t="n">
-        <v>493.5009562</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>403</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-90.50095619999996</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.8166144258425249</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>-0.1075288453179172</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exited at 0.82X </t>
+          <t>In liquidation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Esyasoft Holding (Debt)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.411765</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.411765</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.47078465</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.05901965000000003</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.143333333333333</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.09898188170804081</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mena Mobile Inc (Debt)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Written-off</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Loan</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>2.353982</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.353982</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-2.353982</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>In liquidation</t>
+          <t>Exited. Received payment of $470,784.65 ($411K+$59K)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Jysan Technologies</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>A (Ordinary Shares)</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>20</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.09882450563949773</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Esyasoft Holding (Debt)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Loan</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>0.411765</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.411765</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.47078465</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.05901965000000003</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.143333333333333</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.09898188170804081</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Exited. Received payment of $470,784.65 ($411K+$59K)</t>
+          <t>Exited at $24.5m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Instadeep Limited</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>B Prefs</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>5.023720198477434</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.023720198477434</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7.942192529999999</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.918472331522565</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.580938471136805</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.3280349790276135</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Jysan Technologies</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>A (Ordinary Shares)</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K33" t="n">
-        <v>20</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.09882450563949773</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Exited at $24.5m</t>
+          <t>Exited at 1.56X | Residual Value = 0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Esyasoft Holding</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Convertible Note</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.3609176591261273</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Instadeep Limited</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>B Prefs</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>5.023720198477434</v>
-      </c>
-      <c r="K34" t="n">
-        <v>5.023720198477434</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>7.942192529999998</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.918472331522564</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.580938471136805</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.3280349790276135</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Exited at 1.56X | Residual Value = 0</t>
+          <t>Exited at $5m (10th May) | Residual value = 0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mena Mobile Inc</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Written-off</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>B Prefs</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Esyasoft Holding</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Convertible Note</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.3609176591261273</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Exited at $5m (10th May) | Residual value = 0</t>
+          <t>As per 3rd Party | Ardent Estimates | Equity written off</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9607,7 +12790,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mena Mobile Inc</t>
+          <t>Glass Earth Holdings LLC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9627,7 +12810,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>B Prefs</t>
+          <t>Promissory Note</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -9659,19 +12842,19 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>As per 3rd Party | Ardent Estimates | Equity written off</t>
+          <t>In default</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9686,7 +12869,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Glass Earth Holdings LLC</t>
+          <t>Jollychic Holding Limited</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9706,14 +12889,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Promissory Note</t>
+          <t>C+ Prefs</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9725,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>-8</v>
+        <v>-65</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -9738,209 +12921,211 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>In default</t>
+          <t>Exited/Liquidated</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Honor Device Co Ltd</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>G42</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Equity-TBC</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>800</v>
+      </c>
+      <c r="K38" t="n">
+        <v>800</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>802.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.799999999999955</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.0035</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.002935923132959731</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MOZN Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Jollychic Holding Limited</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Written-off</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>C+ Prefs</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>65</v>
-      </c>
-      <c r="K38" t="n">
-        <v>65</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-65</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Exited/Liquidated</t>
+          <t>Exited at 1.0X</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Exited</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>G42 Investments AI Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sinovation Disrupt Fund, L.P.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>G42 Investments</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>50</v>
+      </c>
+      <c r="K39" t="n">
+        <v>24.959693</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>25.40352135</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.4438283500000004</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.017781803245737</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.007642245213040634</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>Exited</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Honor Device Co Ltd</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>G42</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Equity-TBC</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>800</v>
-      </c>
-      <c r="K39" t="n">
-        <v>800</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>802.8</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.799999999999955</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.0035</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.002935923132959731</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Exited at 1.0X</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Exited</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sinovation Disrupt Fund, L.P.</t>
+          <t>MGX I LP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>G42 Investments</t>
+          <t>G42 Holding</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9949,39 +13134,29 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>41.967904</v>
+        <v>1524.145076</v>
       </c>
       <c r="K40" t="n">
-        <v>41.967904</v>
+        <v>350.846909</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1173.298167</v>
       </c>
       <c r="M40" t="n">
-        <v>42.41173234999999</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>948.484252</v>
       </c>
       <c r="O40" t="n">
-        <v>0.4438283499999969</v>
+        <v>597.637343</v>
       </c>
       <c r="P40" t="n">
-        <v>1.010575423304438</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.007642245213040634</v>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Exited</t>
-        </is>
-      </c>
+        <v>2.703413448057483</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10177,17 +13352,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Acies Investments Fund I, L.P.</t>
+          <t>Cerebras Systems Inc (1)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -10212,40 +13387,40 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>17.1125</v>
+        <v>39.99998336</v>
       </c>
       <c r="K2" t="n">
-        <v>17.1125</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="M2" t="n">
-        <v>15.7263875</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="N2" t="n">
-        <v>15.7263875</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.386112500000001</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.386112500000001</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -10257,40 +13432,40 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>12.683716</v>
+        <v>286.4823928099999</v>
       </c>
       <c r="W2" t="n">
-        <v>14.034903</v>
+        <v>265.62083464</v>
       </c>
       <c r="X2" t="n">
-        <v>1.351186999999999</v>
+        <v>-20.86155816999991</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.042671499999999</v>
+        <v>246.4824094499999</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.6914845</v>
+        <v>225.62085128</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.351186999999999</v>
+        <v>-20.86155816999988</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8065244481607744</v>
+        <v>7.162062799668123</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8924429084556132</v>
+        <v>6.640523628457831</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.08591846029483885</v>
+        <v>-0.5215391712102928</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.05492458454080403</v>
+        <v>0.5091940466191891</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02935277732578557</v>
+        <v>0.5091940466191891</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.02557180721501846</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -10306,17 +13481,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc (1)</t>
+          <t>Cerebras Systems Inc (2)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10341,37 +13516,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Capital SPV RSC Ltd</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Capital SPV RSC Ltd</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>39.99998336</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>39.99998336</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-6.938893903907228e-18</v>
       </c>
       <c r="M3" t="n">
-        <v>39.99998335999999</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>39.99998335999999</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-6.938893903907228e-18</v>
       </c>
       <c r="P3" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -10386,41 +13561,31 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>318.618131</v>
+        <v>698.16579661</v>
       </c>
       <c r="W3" t="n">
-        <v>286.4823928099999</v>
+        <v>647.32558184</v>
       </c>
       <c r="X3" t="n">
-        <v>-32.1357381900001</v>
+        <v>-50.84021476999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>278.61814764</v>
+        <v>698.1306617</v>
       </c>
       <c r="Z3" t="n">
-        <v>246.4824094499999</v>
+        <v>647.29044693</v>
       </c>
       <c r="AA3" t="n">
-        <v>-32.1357381900001</v>
+        <v>-50.84021476999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.965456588629942</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.162062799668123</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.8033937889618183</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.5552594721409149</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.5091940466191891</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.04606542552172577</v>
-      </c>
+        <v>19871</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -10435,17 +13600,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc (2)</t>
+          <t>MGX 1 Strategic Co-invest</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10470,82 +13635,86 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.03513491000000001</v>
+        <v>296.60196</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03513491000000001</v>
+        <v>296.60196</v>
       </c>
       <c r="L4" t="n">
-        <v>-6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03513491000000001</v>
+        <v>562.499557575</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03513491000000001</v>
+        <v>294.251545</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.938893903907228e-18</v>
+        <v>-268.248012575</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-265.897597575</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.350415</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>268.248012575</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>249.9999988</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-249.9999988</v>
       </c>
       <c r="V4" t="n">
-        <v>776.481511</v>
+        <v>1180.373331</v>
       </c>
       <c r="W4" t="n">
-        <v>698.16579661</v>
+        <v>1180.373331</v>
       </c>
       <c r="X4" t="n">
-        <v>-78.31571438999993</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>776.4463760899999</v>
+        <v>867.8737722249999</v>
       </c>
       <c r="Z4" t="n">
-        <v>698.1306617</v>
+        <v>886.1217859999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>-78.31571438999993</v>
+        <v>18.248013775</v>
       </c>
       <c r="AB4" t="n">
-        <v>22100</v>
+        <v>2.542887919710556</v>
       </c>
       <c r="AC4" t="n">
-        <v>19871</v>
+        <v>4.011443103892623</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2229.000000000004</v>
+        <v>1.468555184182067</v>
       </c>
       <c r="AE4" t="n">
-        <v>3819889612.178071</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+        <v>1.148844186667105</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.148844186667105</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -10553,24 +13722,24 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>invested, remaining_commitment, distributions, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DriveNets</t>
+          <t>MGX I Denali Holding LP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10585,95 +13754,95 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partially Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Partially Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>300</v>
+        <v>35.652964</v>
       </c>
       <c r="K5" t="n">
-        <v>300</v>
+        <v>35.652964</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>300</v>
+        <v>27.67275042834596</v>
       </c>
       <c r="N5" t="n">
-        <v>300</v>
+        <v>35.652964</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>7.980213571654037</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>7.980213571654037</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-7.980213571654037</v>
       </c>
       <c r="S5" t="n">
-        <v>84.80448613999999</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>84.80448613999999</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>506.5024466568</v>
+        <v>62.794035</v>
       </c>
       <c r="W5" t="n">
-        <v>497.5350567066</v>
+        <v>62.794035</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.967389950199959</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>291.3069327968</v>
+        <v>35.12128457165404</v>
       </c>
       <c r="Z5" t="n">
-        <v>282.3395428466</v>
+        <v>27.141071</v>
       </c>
       <c r="AA5" t="n">
-        <v>-8.967389950200015</v>
+        <v>-7.980213571654033</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.971023109322667</v>
+        <v>2.269164937637653</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.941131809488667</v>
+        <v>1.761257072483511</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.02989129983400041</v>
+        <v>-0.507907865154142</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1821719849102789</v>
+        <v>0.7757347398913037</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1745459048509513</v>
+        <v>0.7757347398913037</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.007626080059327578</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -10682,24 +13851,24 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>carrying_value, gain</t>
+          <t>invested, remaining_commitment, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MGX 1 Strategic Co-invest</t>
+          <t>MGX I LP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10733,77 +13902,73 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>296.60196</v>
+        <v>1524.145076</v>
       </c>
       <c r="K6" t="n">
-        <v>296.60196</v>
+        <v>1524.145076</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>562.4995575749999</v>
+        <v>437.0838774046402</v>
       </c>
       <c r="N6" t="n">
-        <v>562.499557575</v>
+        <v>350.846909</v>
       </c>
       <c r="O6" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>-86.23696840464021</v>
       </c>
       <c r="P6" t="n">
-        <v>-265.8975975749999</v>
+        <v>1087.06119859536</v>
       </c>
       <c r="Q6" t="n">
-        <v>-265.897597575</v>
+        <v>1173.298167</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>86.23696840463981</v>
       </c>
       <c r="S6" t="n">
-        <v>249.9999988</v>
+        <v>91.05395026651516</v>
       </c>
       <c r="T6" t="n">
-        <v>249.9999988</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>-91.05395026651516</v>
       </c>
       <c r="V6" t="n">
-        <v>741.8567860000001</v>
+        <v>948.484252</v>
       </c>
       <c r="W6" t="n">
-        <v>1180.373331</v>
+        <v>948.484252</v>
       </c>
       <c r="X6" t="n">
-        <v>438.516545</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>429.3572272250001</v>
+        <v>602.454324861875</v>
       </c>
       <c r="Z6" t="n">
-        <v>867.8737722249999</v>
+        <v>597.637343</v>
       </c>
       <c r="AA6" t="n">
-        <v>438.5165449999998</v>
+        <v>-4.816981861874979</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.763302337651621</v>
+        <v>2.378349456491481</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.542887919710556</v>
+        <v>2.703413448057483</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.779585582058935</v>
+        <v>0.3250639915660019</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6452389979024198</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.148844186667105</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.5036051887646855</v>
-      </c>
+        <v>1.608035438909162</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -10811,24 +13976,24 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>invested, remaining_commitment, distributions, gain, tvpi, irr</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MGX I Denali Holding LP</t>
+          <t>New Space Capital Fund I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10853,82 +14018,86 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>35.652964</v>
+        <v>26.7196311505</v>
       </c>
       <c r="K7" t="n">
-        <v>35.652964</v>
+        <v>26.7823643474</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.06273319689999823</v>
       </c>
       <c r="M7" t="n">
-        <v>27.67275042834596</v>
+        <v>17.80166535</v>
       </c>
       <c r="N7" t="n">
-        <v>27.67275042834596</v>
+        <v>16.87804819658807</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.9236171534119322</v>
       </c>
       <c r="P7" t="n">
-        <v>7.980213571654037</v>
+        <v>8.917965800499999</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.980213571654037</v>
+        <v>9.904316150811932</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9863503503119322</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>6.50828684</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>6.7779339379808</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2696470979807994</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>54.1676251908</v>
       </c>
       <c r="W7" t="n">
-        <v>62.794035</v>
+        <v>57.15618120708599</v>
       </c>
       <c r="X7" t="n">
-        <v>62.794035</v>
+        <v>2.988556016285983</v>
       </c>
       <c r="Y7" t="n">
-        <v>-27.67275042834596</v>
+        <v>42.87424668079999</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.12128457165404</v>
+        <v>47.05606694847872</v>
       </c>
       <c r="AA7" t="n">
-        <v>62.79403500000001</v>
+        <v>4.181820267678724</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.408440212634375</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.269164937637653</v>
+        <v>3.788004063052219</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.269164937637653</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
+        <v>0.3795638504178442</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1994548830844582</v>
+      </c>
       <c r="AF7" t="n">
-        <v>0.7757347398913037</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
+        <v>0.1994548830844582</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.775557561562891e-17</v>
+      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -10936,24 +14105,24 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>committed, invested, remaining_commitment, distributions, carrying_value, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MGX I LP</t>
+          <t>New Space Capital GP Com SCSp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10978,85 +14147,85 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1524.145076</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="K8" t="n">
-        <v>1524.145076</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>437.0838774046402</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="N8" t="n">
-        <v>437.0838774046402</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1087.06119859536</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1087.06119859536</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>91.05395026651516</v>
+        <v>0.20616173</v>
       </c>
       <c r="T8" t="n">
-        <v>91.05395026651516</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.20616173</v>
       </c>
       <c r="V8" t="n">
-        <v>644.14725737</v>
+        <v>3.858379496274193</v>
       </c>
       <c r="W8" t="n">
-        <v>948.484252</v>
+        <v>6.786449200178311</v>
       </c>
       <c r="X8" t="n">
-        <v>304.3369946299999</v>
+        <v>2.928069703904118</v>
       </c>
       <c r="Y8" t="n">
-        <v>298.117330231875</v>
+        <v>1.358658873333016</v>
       </c>
       <c r="Z8" t="n">
-        <v>602.454324861875</v>
+        <v>4.080566847237135</v>
       </c>
       <c r="AA8" t="n">
-        <v>304.33699463</v>
+        <v>2.721907973904119</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.682059773062474</v>
+        <v>1.502113061883941</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.378349456491481</v>
+        <v>2.508035573978941</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.6962896834290071</v>
+        <v>1.005922512095</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8586539373442278</v>
+        <v>0.1156541964277766</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.608035438909162</v>
+        <v>0.1156541964277766</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.7493815015649344</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -11065,24 +14234,24 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>distributions, carrying_value, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New Space Capital Fund I</t>
+          <t>North Summit Capital Fund</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -11116,76 +14285,76 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>26.7196311505</v>
+        <v>83.361611</v>
       </c>
       <c r="K9" t="n">
-        <v>26.7196311505</v>
+        <v>83.361611</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>17.80166535</v>
+        <v>83.361611</v>
       </c>
       <c r="N9" t="n">
-        <v>17.80166535</v>
+        <v>83.361611</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>8.917965800499999</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.917965800499999</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>6.50828684</v>
+        <v>7.875571</v>
       </c>
       <c r="T9" t="n">
-        <v>6.50828684</v>
+        <v>7.875571</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>26.095994627985</v>
+        <v>69.98505299999999</v>
       </c>
       <c r="W9" t="n">
-        <v>54.1676251908</v>
+        <v>72.566225</v>
       </c>
       <c r="X9" t="n">
-        <v>28.071630562815</v>
+        <v>2.581172000000009</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.802616117985</v>
+        <v>-5.500987000000009</v>
       </c>
       <c r="Z9" t="n">
-        <v>42.87424668079999</v>
+        <v>-2.919815</v>
       </c>
       <c r="AA9" t="n">
-        <v>28.07163056281499</v>
+        <v>2.581172000000009</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.831529849985917</v>
+        <v>0.9340105483326131</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.408440212634375</v>
+        <v>0.9649741054068641</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.576910362648458</v>
+        <v>0.03096355707425102</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.07373103259662646</v>
+        <v>-0.01242878543472056</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1994548830844582</v>
+        <v>-0.01242878543472056</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1257238504878317</v>
+        <v>1.734723475976807e-18</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -11194,24 +14363,24 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>carrying_value, gain</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New Space Capital GP Com SCSp</t>
+          <t>ONT plc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -11236,28 +14405,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="K10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="N10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -11272,49 +14441,49 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.20616173</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.20616173</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.655776071404095</v>
+        <v>67.52236550879999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.858379496274193</v>
+        <v>105.22733244336</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2026034248700976</v>
+        <v>37.70496693456001</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.156055448462918</v>
+        <v>-73.94789416556648</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.358658873333016</v>
+        <v>-36.2429272310065</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2026034248700983</v>
+        <v>37.70496693455998</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4272378831276</v>
+        <v>0.4772901786157859</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.502113061883941</v>
+        <v>0.743812393400353</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.07487517875634087</v>
+        <v>0.2665222147845671</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1074641933261324</v>
+        <v>-0.1135171173653592</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1156541964277766</v>
+        <v>-0.1135171173653592</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.008190003101644208</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -11330,66 +14499,66 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ONT plc</t>
+          <t>Sinovation Disrupt Fund, L.P.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>141.4702596743665</v>
+        <v>41.967904</v>
       </c>
       <c r="K11" t="n">
-        <v>141.4702596743665</v>
+        <v>50</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>8.032096000000003</v>
       </c>
       <c r="M11" t="n">
-        <v>141.4702596743665</v>
+        <v>41.967904</v>
       </c>
       <c r="N11" t="n">
-        <v>141.4702596743665</v>
+        <v>24.959693</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-17.008211</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -11401,49 +14570,49 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>42.41173234999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>25.40352135</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-17.00821099999999</v>
       </c>
       <c r="V11" t="n">
-        <v>72.94484711592</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>67.52236550879999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.422481607120005</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-68.5254125584465</v>
+        <v>0.4438283499999969</v>
       </c>
       <c r="Z11" t="n">
-        <v>-73.94789416556648</v>
+        <v>0.4438283500000004</v>
       </c>
       <c r="AA11" t="n">
-        <v>-5.422481607119977</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5156196594522625</v>
+        <v>1.010575423304438</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4772901786157859</v>
+        <v>1.017781803245737</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.03832948083647658</v>
+        <v>0.007206379941299135</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.1036411286787608</v>
+        <v>0.007642245213040634</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.1135171173653592</v>
+        <v>0.007642245213040634</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.009875988686598405</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -11452,34 +14621,34 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>carrying_value, gain</t>
+          <t>committed, invested, distributions</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verses AI Inc</t>
+          <t>WLD Tokens</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11494,28 +14663,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -11530,46 +14699,46 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1338020955555556</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1338020955555556</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-9.866197904444444</v>
+        <v>99.99312500000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>-10</v>
+        <v>99.99312500000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.1338020955555557</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01338020955555556</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.01338020955555556</v>
-      </c>
+        <v>14545.45454545455</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>-0.8809058327281951</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
+        <v>727.8222082232667</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>727.8222082232667</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -11577,19 +14746,19 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>carrying_value, gain, irr</t>
+          <t>tvpi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11664,40 +14833,40 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9.776086049999998</v>
+        <v>8.399903950000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.399903950000001</v>
+        <v>8.309024000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.376182099999998</v>
+        <v>-0.09087994999999971</v>
       </c>
       <c r="Y13" t="n">
-        <v>-14.75516395</v>
+        <v>-16.13134605</v>
       </c>
       <c r="Z13" t="n">
-        <v>-16.13134605</v>
+        <v>-16.222226</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.376182099999998</v>
+        <v>-0.09087994999999793</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3985156096815286</v>
+        <v>0.3424164667515924</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3424164667515924</v>
+        <v>0.3387118063694268</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.05609914292993623</v>
+        <v>-0.003704660382165603</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.2201095569344076</v>
+        <v>-0.246693162941984</v>
       </c>
       <c r="AF13" t="n">
         <v>-0.246693162941984</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02658360600757637</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -11706,7 +14875,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi</t>
+          <t>carrying_value, gain</t>
         </is>
       </c>
     </row>
